--- a/debug/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/Llama-3.1-8B-Instruct/default/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/Llama-3.1-8B-Instruct/default/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>7</v>
+        <v>72</v>
       </c>
       <c r="D2">
-        <v>3</v>
+        <v>95</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>77</v>
       </c>
       <c r="G2">
-        <v>414</v>
+        <v>182</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>7</v>
+        <v>143</v>
       </c>
       <c r="D3">
-        <v>5</v>
+        <v>56</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>58</v>
       </c>
       <c r="G3">
-        <v>409</v>
+        <v>169</v>
       </c>
       <c r="H3">
         <v>426</v>

--- a/debug/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/Llama-3.1-8B-Instruct/default/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/Llama-3.1-8B-Instruct/default/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="D2">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E2">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="G2">
-        <v>182</v>
+        <v>220</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>143</v>
+        <v>106</v>
       </c>
       <c r="D3">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="E3">
-        <v>58</v>
+        <v>31</v>
       </c>
       <c r="G3">
-        <v>169</v>
+        <v>244</v>
       </c>
       <c r="H3">
         <v>426</v>
